--- a/backend/wp_templates/K/K1 其他应收款.xlsx
+++ b/backend/wp_templates/K/K1 其他应收款.xlsx
@@ -34068,7 +34068,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="419">
-        <f>D11+SUM(G11:G11)-SUM(I11:K11)</f>
+        <f>J11+K11</f>
         <v>0</v>
       </c>
       <c r="M11" s="407"/>
